--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>28-Jul 18:31</t>
+          <t>28-Jul 19:28</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.53x</t>
+          <t>20.17x</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>28-Jul 19:28</t>
+          <t>29-Jul 11:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹300 (99.67%) 195 ↓ / 300 ↑</t>
+          <t>₹275 (91.36%) 195 ↓ / 300 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20.17x</t>
+          <t>61.5x</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>29-Jul 11:00</t>
+          <t>29-Jul 16:35</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -486,30 +486,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Poojaa Precision Engg. BSE SMEO</t>
+          <t>Anawil Wire &amp; Engineering NSE SMEU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹275 (91.36%) 195 ↓ / 300 ↑</t>
+          <t>₹60 (22.22%) 60 ↓ / 60 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>61.5x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹159.83 Cr</t>
+          <t>₹177.81 Cr</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -517,27 +517,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>28-Jul GMP: 300</t>
+          <t>3-Aug</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30-Jul</t>
+          <t>5-Aug</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>31-Jul</t>
+          <t>6-Aug</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>29-Jul 16:35</t>
+          <t>30-Jul 10:57</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹60 (22.22%) 60 ↓ / 60 ↑</t>
+          <t>₹70 (25.93%) 60 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>30-Jul 10:57</t>
+          <t>30-Jul 16:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>30-Jul 16:37</t>
+          <t>30-Jul 18:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹70 (25.93%) 60 ↓ / 70 ↑</t>
+          <t>₹65 (24.07%) 60 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>30-Jul 18:55</t>
+          <t>31-Jul 11:31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>31-Jul 11:31</t>
+          <t>31-Jul 16:31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,61 +486,124 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>LAPL Automotive BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹22 (23.40%) 22 ↓ / 22 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>94</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹32.40 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>6-Aug</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10-Aug</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>11-Aug</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>13-Aug</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1-Aug 10:28</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Anawil Wire &amp; Engineering NSE SMEU</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹65 (24.07%) 60 ↓ / 70 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹80 (29.63%) 60 ↓ / 80 ↑</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>270</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>₹177.81 Cr</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G3" t="n">
         <v>400</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>3-Aug</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>5-Aug</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>6-Aug</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>10-Aug</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>31-Jul 16:31</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1-Aug 10:33</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹22 (23.40%) 22 ↓ / 22 ↑</t>
+          <t>₹25 (26.60%) 22 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1-Aug 10:28</t>
+          <t>1-Aug 15:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹80 (29.63%) 60 ↓ / 80 ↑</t>
+          <t>₹90 (33.33%) 60 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -600,10 +600,73 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1-Aug 10:33</t>
+          <t>1-Aug 15:57</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>G.V. Electricals BSE SMEO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2.3x</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>130</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>₹42.25 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>31-Jul GMP: 25</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4-Aug</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5-Aug</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7-Aug</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1-Aug 15:53</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1-Aug 15:55</t>
+          <t>2-Aug 10:57</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1-Aug 15:57</t>
+          <t>2-Aug 10:53</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1-Aug 15:53</t>
+          <t>2-Aug 10:54</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2-Aug 10:57</t>
+          <t>2-Aug 15:57</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2-Aug 10:53</t>
+          <t>2-Aug 15:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2-Aug 10:54</t>
+          <t>2-Aug 15:58</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2-Aug 15:57</t>
+          <t>3-Aug 11:58</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -549,12 +549,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMEU</t>
+          <t>Anawil Wire &amp; Engineering NSE SMEO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹90 (33.33%) 60 ↓ / 90 ↑</t>
+          <t>₹80 (29.63%) 60 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.05x</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3-Aug</t>
+          <t>3-Aug GMP: 80</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2-Aug 15:55</t>
+          <t>3-Aug 12:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.3x</t>
+          <t>10.92x</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2-Aug 15:58</t>
+          <t>3-Aug 12:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3-Aug 11:58</t>
+          <t>3-Aug 17:31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.05x</t>
+          <t>4.77x</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3-Aug 12:02</t>
+          <t>3-Aug 17:33</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10.92x</t>
+          <t>22.13x</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>3-Aug 12:02</t>
+          <t>3-Aug 17:31</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹25 (26.60%) 22 ↓ / 25 ↑</t>
+          <t>₹27 (28.72%) 22 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3-Aug 17:31</t>
+          <t>4-Aug 10:56</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.77x</t>
+          <t>6.37x</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3-Aug 17:33</t>
+          <t>4-Aug 10:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -612,7 +612,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEO</t>
+          <t>G.V. Electricals BSE SMECT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>22.13x</t>
+          <t>37.95x</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4-Aug</t>
+          <t>4-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>3-Aug 17:31</t>
+          <t>4-Aug 11:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4-Aug 10:56</t>
+          <t>4-Aug 16:28</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.37x</t>
+          <t>10.95x</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -600,73 +600,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4-Aug 10:55</t>
+          <t>4-Aug 16:35</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>G.V. Electricals BSE SMECT</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>37.95x</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>130</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹42.25 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>31-Jul GMP: 25</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4-Aug GMP: 26</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>5-Aug</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>7-Aug</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>4-Aug 11:02</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4-Aug 16:28</t>
+          <t>5-Aug 11:01</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -549,7 +549,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMEO</t>
+          <t>Anawil Wire &amp; Engineering NSE SMECT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10.95x</t>
+          <t>25.02x</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5-Aug</t>
+          <t>5-Aug GMP: 80</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4-Aug 16:35</t>
+          <t>5-Aug 10:56</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹27 (28.72%) 22 ↓ / 27 ↑</t>
+          <t>₹26 (27.66%) 22 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5-Aug 11:01</t>
+          <t>5-Aug 16:34</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25.02x</t>
+          <t>148.89x</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5-Aug 10:56</t>
+          <t>5-Aug 16:28</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMEU</t>
+          <t>LAPL Automotive BSE SMEO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹26 (27.66%) 22 ↓ / 27 ↑</t>
+          <t>₹30 (31.91%) 22 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>6-Aug GMP: 30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5-Aug 16:34</t>
+          <t>6-Aug 10:56</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -549,12 +549,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anawil Wire &amp; Engineering NSE SMECT</t>
+          <t>G.V. Electricals BSE SMEO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹80 (29.63%) 60 ↓ / 90 ↑</t>
+          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -564,43 +564,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>148.89x</t>
+          <t>146.76x</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>270</v>
+        <v>130</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹177.81 Cr</t>
+          <t>₹42.25 Cr</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3-Aug GMP: 80</t>
+          <t>31-Jul GMP: 25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5-Aug GMP: 80</t>
+          <t>7-Aug</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6-Aug</t>
+          <t>10-Aug</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>12-Aug</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5-Aug 16:28</t>
+          <t>6-Aug 11:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.27x</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6-Aug 10:56</t>
+          <t>6-Aug 16:31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6-Aug 11:02</t>
+          <t>6-Aug 16:29</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹30 (31.91%) 22 ↓ / 30 ↑</t>
+          <t>₹32 (34.04%) 22 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.27x</t>
+          <t>5.99x</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -517,7 +517,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 30</t>
+          <t>6-Aug GMP: 32</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6-Aug 16:31</t>
+          <t>7-Aug 9:56</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -549,7 +549,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G.V. Electricals BSE SMEO</t>
+          <t>G.V. Electricals BSE SMECT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7-Aug</t>
+          <t>7-Aug GMP: 26</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6-Aug 16:29</t>
+          <t>7-Aug 9:57</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.99x</t>
+          <t>25.88x</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7-Aug 9:56</t>
+          <t>7-Aug 15:34</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>146.76x</t>
+          <t>165.62x</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7-Aug 9:57</t>
+          <t>7-Aug 15:32</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>25.88x</t>
+          <t>31.41x</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -537,73 +537,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7-Aug 15:34</t>
+          <t>8-Aug 9:29</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>G.V. Electricals BSE SMECT</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹26 (20.00%) 18 ↓ / 26 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>165.62x</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>130</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹42.25 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>31-Jul GMP: 25</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7-Aug GMP: 26</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>10-Aug</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>12-Aug</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>7-Aug 15:32</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹32 (34.04%) 22 ↓ / 32 ↑</t>
+          <t>₹35 (37.23%) 22 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8-Aug 9:29</t>
+          <t>8-Aug 14:58</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8-Aug 14:58</t>
+          <t>9-Aug 9:28</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>9-Aug 9:28</t>
+          <t>9-Aug 14:53</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMEO</t>
+          <t>LAPL Automotive BSE SMECT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹35 (37.23%) 22 ↓ / 35 ↑</t>
+          <t>₹37 (39.36%) 22 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>31.41x</t>
+          <t>42.89x</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -522,7 +522,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10-Aug</t>
+          <t>10-Aug GMP: 37</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>9-Aug 14:53</t>
+          <t>10-Aug 9:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹37 (39.36%) 22 ↓ / 37 ↑</t>
+          <t>₹39 (41.49%) 22 ↓ / 39 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.89x</t>
+          <t>332.33x</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -522,7 +522,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 37</t>
+          <t>10-Aug GMP: 39</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10-Aug 9:55</t>
+          <t>10-Aug 15:35</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LAPL Automotive BSE SMECT</t>
+          <t>Technocrats Plasma Systems BSE SMEU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹39 (41.49%) 22 ↓ / 39 ↑</t>
+          <t>₹30 (22.73%) 30 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,43 +501,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>332.33x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹32.40 Cr</t>
+          <t>₹60.98 Cr</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6-Aug GMP: 32</t>
+          <t>14-Aug</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10-Aug GMP: 39</t>
+          <t>18-Aug</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11-Aug</t>
+          <t>19-Aug</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>21-Aug</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10-Aug 15:35</t>
+          <t>11-Aug 9:28</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,69 +480,6 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Technocrats Plasma Systems BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹30 (22.73%) 30 ↓ / 30 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>132</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>₹60.98 Cr</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>14-Aug</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>18-Aug</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>19-Aug</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>21-Aug</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>11-Aug 9:28</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,69 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Credent Connect NSE SMEU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹50 (26.46%) 35 ↓ / 50 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>189</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹93.90 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>13-Aug</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>17-Aug</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>18-Aug</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>20-Aug</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>12-Aug 15:32</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEU</t>
+          <t>Credent Connect NSE SMEO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.05x</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -517,7 +517,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13-Aug</t>
+          <t>13-Aug GMP: 50</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>12-Aug 15:32</t>
+          <t>13-Aug 9:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹50 (26.46%) 35 ↓ / 50 ↑</t>
+          <t>₹62 (32.80%) 35 ↓ / 62 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.05x</t>
+          <t>1.76x</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -517,7 +517,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 50</t>
+          <t>13-Aug GMP: 62</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>13-Aug 9:55</t>
+          <t>13-Aug 15:28</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹62 (32.80%) 35 ↓ / 62 ↑</t>
+          <t>₹75 (39.68%) 35 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.76x</t>
+          <t>2.18x</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -517,7 +517,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13-Aug GMP: 62</t>
+          <t>13-Aug GMP: 75</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>13-Aug 15:28</t>
+          <t>14-Aug 9:31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.18x</t>
+          <t>10.3x</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>14-Aug 9:31</t>
+          <t>14-Aug 15:36</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,61 +486,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Technocrats Plasma Systems BSE SMEO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹30 (22.73%) 12 ↓ / 30 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.42x</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹60.98 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>14-Aug GMP: 30</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>18-Aug</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19-Aug</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>21-Aug</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>15-Aug 9:02</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Credent Connect NSE SMEO</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹75 (39.68%) 35 ↓ / 75 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹65 (34.39%) 35 ↓ / 75 ↑</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>10.3x</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>189</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>12.14x</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>₹93.90 Cr</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>600</v>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>13-Aug GMP: 75</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>17-Aug</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>18-Aug</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>20-Aug</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>14-Aug 15:36</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>15-Aug 9:02</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹30 (22.73%) 12 ↓ / 30 ↑</t>
+          <t>₹32 (24.24%) 12 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>15-Aug 9:02</t>
+          <t>15-Aug 14:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹65 (34.39%) 35 ↓ / 75 ↑</t>
+          <t>₹55 (29.10%) 35 ↓ / 75 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15-Aug 9:02</t>
+          <t>15-Aug 15:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>15-Aug 14:55</t>
+          <t>16-Aug 8:54</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15-Aug 15:02</t>
+          <t>16-Aug 9:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16-Aug 8:54</t>
+          <t>16-Aug 14:59</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-Aug 9:00</t>
+          <t>16-Aug 14:56</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16-Aug 14:59</t>
+          <t>17-Aug 9:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Credent Connect NSE SMEO</t>
+          <t>Credent Connect NSE SMECT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>17-Aug</t>
+          <t>17-Aug GMP: 55</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-Aug 14:56</t>
+          <t>17-Aug 8:54</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹32 (24.24%) 12 ↓ / 32 ↑</t>
+          <t>₹30 (22.73%) 12 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.42x</t>
+          <t>3.95x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>17-Aug 9:00</t>
+          <t>17-Aug 14:56</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12.14x</t>
+          <t>130.04x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>17-Aug 8:54</t>
+          <t>17-Aug 14:58</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Technocrats Plasma Systems BSE SMEO</t>
+          <t>Technocrats Plasma Systems BSE SMECT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.95x</t>
+          <t>5.71x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>18-Aug</t>
+          <t>18-Aug GMP: 30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -541,77 +541,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>17-Aug 14:56</t>
+          <t>18-Aug 9:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Credent Connect NSE SMECT</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹55 (29.10%) 35 ↓ / 75 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>130.04x</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹93.90 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>13-Aug GMP: 75</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>17-Aug GMP: 55</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>18-Aug</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>20-Aug</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>17-Aug 14:58</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹30 (22.73%) 12 ↓ / 32 ↑</t>
+          <t>₹43 (32.58%) 12 ↓ / 43 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.71x</t>
+          <t>152.88x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>18-Aug GMP: 30</t>
+          <t>18-Aug GMP: 43</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>18-Aug 9:00</t>
+          <t>18-Aug 14:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,73 +480,6 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Technocrats Plasma Systems BSE SMECT</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹43 (32.58%) 12 ↓ / 43 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>152.88x</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>₹60.98 Cr</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>14-Aug GMP: 30</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>18-Aug GMP: 43</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>19-Aug</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>21-Aug</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>18-Aug 14:55</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,73 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sumax Engineering NSE SMEU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹30 (29.70%) 20 ↓ / 30 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹53.40 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>25-Aug</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>28-Aug</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>31-Aug</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2-Sep</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>20-Aug 8:56</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20-Aug 8:56</t>
+          <t>20-Aug 14:54</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹30 (29.70%) 20 ↓ / 30 ↑</t>
+          <t>₹32 (31.68%) 20 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20-Aug 14:54</t>
+          <t>21-Aug 8:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>21-Aug 8:37</t>
+          <t>21-Aug 14:57</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,65 +486,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Kwick Forensic Solutions BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹43 (47.78%) 15 ↓ / 43 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹50.77 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>27-Aug</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>31-Aug</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1-Sep</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3-Sep</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>22-Aug 9:00</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Sumax Engineering NSE SMEU</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>₹32 (31.68%) 20 ↓ / 32 ↑</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>₹53.40 Cr</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>25-Aug</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>28-Aug</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>31-Aug</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2-Sep</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>21-Aug 14:57</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>22-Aug 9:00</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>22-Aug 9:00</t>
+          <t>22-Aug 14:53</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>22-Aug 9:00</t>
+          <t>22-Aug 15:01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹43 (47.78%) 15 ↓ / 43 ↑</t>
+          <t>₹51 (56.67%) 15 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>22-Aug 14:53</t>
+          <t>23-Aug 8:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>22-Aug 15:01</t>
+          <t>23-Aug 8:56</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹51 (56.67%) 15 ↓ / 51 ↑</t>
+          <t>₹61 (67.78%) 15 ↓ / 61 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23-Aug 8:55</t>
+          <t>23-Aug 14:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>23-Aug 8:56</t>
+          <t>23-Aug 14:56</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23-Aug 14:55</t>
+          <t>24-Aug 8:56</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>23-Aug 14:56</t>
+          <t>24-Aug 9:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>24-Aug 8:56</t>
+          <t>24-Aug 14:53</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24-Aug 9:02</t>
+          <t>24-Aug 14:54</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,17 +486,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMEU</t>
+          <t>Shanti Inorganics NSE SMEU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹61 (67.78%) 15 ↓ / 61 ↑</t>
+          <t>₹25 (30.12%) 25 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹50.77 Cr</t>
+          <t>₹47.24 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -521,27 +521,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>24-Aug 14:53</t>
+          <t>25-Aug 9:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,65 +553,199 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sumax Engineering NSE SMEU</t>
+          <t>Paluck Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>₹10 (20.83%) 10 ↓ / 10 ↑</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹33.00 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>28-Aug</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1-Sep</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2-Sep</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4-Sep</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>25-Aug 9:01</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kwick Forensic Solutions BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹64 (71.11%) 15 ↓ / 64 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>₹50.77 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>27-Aug</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>31-Aug</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1-Sep</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>3-Sep</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>25-Aug 9:01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sumax Engineering NSE SMEO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>₹32 (31.68%) 20 ↓ / 32 ↑</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>₹53.40 Cr</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>25-Aug</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>25-Aug GMP: 32</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>28-Aug</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>31-Aug</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2-Sep</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>24-Aug 14:54</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>25-Aug 8:58</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>25-Aug 9:00</t>
+          <t>25-Aug 14:59</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25-Aug 9:01</t>
+          <t>25-Aug 14:53</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25-Aug 9:01</t>
+          <t>25-Aug 14:53</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹32 (31.68%) 20 ↓ / 32 ↑</t>
+          <t>₹35 (34.65%) 20 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.31x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>25-Aug GMP: 32</t>
+          <t>25-Aug GMP: 35</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25-Aug 8:58</t>
+          <t>25-Aug 14:58</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹25 (30.12%) 25 ↓ / 25 ↑</t>
+          <t>₹31 (37.35%) 25 ↓ / 31 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>25-Aug 14:59</t>
+          <t>26-Aug 8:57</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹10 (20.83%) 10 ↓ / 10 ↑</t>
+          <t>₹18 (37.50%) 10 ↓ / 18 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25-Aug 14:53</t>
+          <t>26-Aug 8:54</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25-Aug 14:53</t>
+          <t>26-Aug 8:55</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.31x</t>
+          <t>3.24x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>25-Aug 14:58</t>
+          <t>26-Aug 8:54</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>26-Aug 8:57</t>
+          <t>26-Aug 14:32</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,12 +558,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹18 (37.50%) 10 ↓ / 18 ↑</t>
+          <t>₹25 (52.08%) 10 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-Aug 8:54</t>
+          <t>26-Aug 14:34</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>26-Aug 8:55</t>
+          <t>26-Aug 14:33</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹35 (34.65%) 20 ↓ / 35 ↑</t>
+          <t>₹30 (29.70%) 20 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.24x</t>
+          <t>8.15x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>26-Aug 8:54</t>
+          <t>26-Aug 14:29</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>26-Aug 14:32</t>
+          <t>27-Aug 16:36</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,17 +553,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Paluck Technologies BSE SMEU</t>
+          <t>Ashutosh Fibre NSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹25 (52.08%) 10 ↓ / 25 ↑</t>
+          <t>₹37 (40.22%) 13 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -573,42 +573,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹33.00 Cr</t>
+          <t>₹56.35 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>31-Aug</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-Aug 14:34</t>
+          <t>27-Aug 16:31</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMEU</t>
+          <t>Paluck Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹64 (71.11%) 15 ↓ / 64 ↑</t>
+          <t>₹25 (52.08%) 10 ↓ / 25 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -640,42 +640,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹50.77 Cr</t>
+          <t>₹33.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>27-Aug</t>
+          <t>28-Aug</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>1-Sep</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1-Sep</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>26-Aug 14:33</t>
+          <t>27-Aug 16:33</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,65 +687,132 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Kwick Forensic Solutions BSE SMEO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>₹64 (71.11%) 15 ↓ / 64 ↑</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6.45x</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>₹50.77 Cr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>27-Aug GMP: 64</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>31-Aug</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1-Sep</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>3-Sep</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>27-Aug 16:28</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Sumax Engineering NSE SMEO</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>₹30 (29.70%) 20 ↓ / 35 ↑</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>₹25 (24.75%) 20 ↓ / 35 ↑</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8.15x</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>18.84x</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>₹53.40 Cr</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>25-Aug GMP: 35</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>28-Aug</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>31-Aug</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>2-Sep</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>26-Aug 14:29</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>27-Aug 16:30</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27-Aug 16:36</t>
+          <t>27-Aug 19:35</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-Aug 16:31</t>
+          <t>27-Aug 19:35</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>27-Aug 16:33</t>
+          <t>27-Aug 19:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.45x</t>
+          <t>7.51x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>27-Aug 16:28</t>
+          <t>27-Aug 19:33</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>₹25 (24.75%) 20 ↓ / 35 ↑</t>
+          <t>₹35 (34.65%) 20 ↓ / 35 ↑</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18.84x</t>
+          <t>20.8x</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>27-Aug 16:30</t>
+          <t>27-Aug 19:29</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27-Aug 19:35</t>
+          <t>28-Aug 20:34</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-Aug 19:35</t>
+          <t>28-Aug 20:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,7 +620,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Paluck Technologies BSE SMEU</t>
+          <t>Paluck Technologies BSE SMEO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18.18x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>28-Aug</t>
+          <t>28-Aug GMP: 25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>27-Aug 19:37</t>
+          <t>28-Aug 20:32</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.51x</t>
+          <t>20.67x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -742,77 +742,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>27-Aug 19:33</t>
+          <t>28-Aug 20:36</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sumax Engineering NSE SMEO</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>₹35 (34.65%) 20 ↓ / 35 ↑</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>20.8x</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>₹53.40 Cr</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>25-Aug GMP: 35</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>28-Aug</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>31-Aug</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2-Sep</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>27-Aug 19:29</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>28-Aug 20:34</t>
+          <t>29-Aug 14:59</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>28-Aug 20:37</t>
+          <t>29-Aug 14:53</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>28-Aug 20:32</t>
+          <t>29-Aug 14:55</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹64 (71.11%) 15 ↓ / 64 ↑</t>
+          <t>₹70 (77.78%) 15 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>28-Aug 20:36</t>
+          <t>29-Aug 14:55</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>29-Aug 14:59</t>
+          <t>30-Aug 14:28</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>29-Aug 14:53</t>
+          <t>30-Aug 14:32</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>29-Aug 14:55</t>
+          <t>30-Aug 14:34</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>29-Aug 14:55</t>
+          <t>30-Aug 14:30</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>30-Aug 14:28</t>
+          <t>30-Aug 19:31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>30-Aug 14:32</t>
+          <t>30-Aug 19:29</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30-Aug 14:34</t>
+          <t>30-Aug 19:35</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>30-Aug 14:30</t>
+          <t>30-Aug 19:35</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Shanti Inorganics NSE SMEU</t>
+          <t>Ashutosh Fibre NSE SMEO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹31 (37.35%) 25 ↓ / 31 ↑</t>
+          <t>₹37 (40.22%) 13 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,27 +501,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.14x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹47.24 Cr</t>
+          <t>₹56.35 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>31-Aug GMP: 37</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>30-Aug 19:31</t>
+          <t>31-Aug 14:58</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ashutosh Fibre NSE SMEU</t>
+          <t>Shanti Inorganics NSE SMEO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹37 (40.22%) 13 ↓ / 37 ↑</t>
+          <t>₹31 (37.35%) 25 ↓ / 31 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,27 +568,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.85x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>83</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹56.35 Cr</t>
+          <t>₹47.24 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>31-Aug GMP: 31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>30-Aug 19:29</t>
+          <t>31-Aug 14:56</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹25 (52.08%) 10 ↓ / 25 ↑</t>
+          <t>₹30 (62.50%) 10 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18.18x</t>
+          <t>67.54x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30-Aug 19:35</t>
+          <t>31-Aug 15:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kwick Forensic Solutions BSE SMEO</t>
+          <t>Kwick Forensic Solutions BSE SMECT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20.67x</t>
+          <t>154.9x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>31-Aug</t>
+          <t>31-Aug GMP: 70</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>30-Aug 19:35</t>
+          <t>31-Aug 15:01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹37 (40.22%) 13 ↓ / 37 ↑</t>
+          <t>₹27 (29.35%) 13 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.14x</t>
+          <t>4.2x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 37</t>
+          <t>31-Aug GMP: 45</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>31-Aug 14:58</t>
+          <t>1-Sep 13:56</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,199 +553,65 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Shanti Inorganics NSE SMEO</t>
+          <t>Paluck Technologies BSE SMECT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹31 (37.35%) 25 ↓ / 31 ↑</t>
+          <t>₹30 (62.50%) 10 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.85x</t>
+          <t>504.26x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹47.24 Cr</t>
+          <t>₹33.00 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 31</t>
+          <t>28-Aug GMP: 25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>1-Sep GMP: 30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>2-Sep</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>3-Sep</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>7-Sep</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>31-Aug 14:56</t>
+          <t>1-Sep 14:01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Paluck Technologies BSE SMEO</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹30 (62.50%) 10 ↓ / 30 ↑</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>67.54x</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹33.00 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>28-Aug GMP: 25</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1-Sep</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2-Sep</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>4-Sep</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>31-Aug 15:00</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Kwick Forensic Solutions BSE SMECT</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>₹70 (77.78%) 15 ↓ / 70 ↑</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>154.9x</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>₹50.77 Cr</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>27-Aug GMP: 64</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>31-Aug GMP: 70</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1-Sep</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>3-Sep</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>31-Aug 15:01</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ashutosh Fibre NSE SMEO</t>
+          <t>Qualiance International NSE SMEU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹27 (29.35%) 13 ↓ / 45 ↑</t>
+          <t>₹50 (39.37%) 50 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,47 +501,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.2x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>127</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹56.35 Cr</t>
+          <t>₹45.11 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>31-Aug GMP: 45</t>
+          <t>4-Sep</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>8-Sep</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3-Sep</t>
+          <t>9-Sep</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>7-Sep</t>
+          <t>11-Sep</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1-Sep 13:56</t>
+          <t>1-Sep 19:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,62 +553,62 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Paluck Technologies BSE SMECT</t>
+          <t>Ashutosh Fibre NSE SMEO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹30 (62.50%) 10 ↓ / 30 ↑</t>
+          <t>₹20 (21.74%) 13 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>504.26x</t>
+          <t>5.59x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹33.00 Cr</t>
+          <t>₹56.35 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>28-Aug GMP: 25</t>
+          <t>31-Aug GMP: 45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1-Sep GMP: 30</t>
+          <t>2-Sep</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>3-Sep</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>7-Sep</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1-Sep 14:01</t>
+          <t>1-Sep 18:58</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1-Sep 19:00</t>
+          <t>2-Sep 12:56</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ashutosh Fibre NSE SMEO</t>
+          <t>Ashutosh Fibre NSE SMECT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹20 (21.74%) 13 ↓ / 45 ↑</t>
+          <t>₹35 (38.04%) 10 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.59x</t>
+          <t>26.96x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2-Sep</t>
+          <t>2-Sep GMP: 35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -608,10 +608,77 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1-Sep 18:58</t>
+          <t>2-Sep 12:55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Shanti Inorganics NSE SMECT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹25 (30.12%) 25 ↓ / 36 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>51.91x</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>₹47.24 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>31-Aug GMP: 31</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2-Sep GMP: 25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3-Sep</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7-Sep</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2-Sep 12:54</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹50 (39.37%) 50 ↓ / 50 ↑</t>
+          <t>₹55 (43.31%) 50 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,144 +541,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2-Sep 12:56</t>
+          <t>2-Sep 18:33</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ashutosh Fibre NSE SMECT</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹35 (38.04%) 10 ↓ / 45 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>26.96x</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹56.35 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>31-Aug GMP: 45</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2-Sep GMP: 35</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>3-Sep</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>7-Sep</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2-Sep 12:55</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Shanti Inorganics NSE SMECT</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹25 (30.12%) 25 ↓ / 36 ↑</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>51.91x</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹47.24 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>31-Aug GMP: 31</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2-Sep GMP: 25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>3-Sep</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>7-Sep</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2-Sep 12:54</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2-Sep 18:33</t>
+          <t>3-Sep 12:53</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3-Sep 12:53</t>
+          <t>3-Sep 18:31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Qualiance International NSE SMEU</t>
+          <t>Qualiance International NSE SMEO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.19x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4-Sep</t>
+          <t>4-Sep GMP: 55</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3-Sep 18:31</t>
+          <t>4-Sep 13:04</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.19x</t>
+          <t>13.75x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4-Sep 13:04</t>
+          <t>4-Sep 18:36</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13.75x</t>
+          <t>13.78x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4-Sep 18:36</t>
+          <t>5-Sep 12:33</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5-Sep 12:33</t>
+          <t>5-Sep 17:59</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5-Sep 17:59</t>
+          <t>6-Sep 12:54</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6-Sep 12:54</t>
+          <t>6-Sep 17:59</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13.78x</t>
+          <t>58.74x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6-Sep 17:59</t>
+          <t>7-Sep 13:29</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹55 (43.31%) 50 ↓ / 55 ↑</t>
+          <t>₹60 (47.24%) 50 ↓ / 60 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58.74x</t>
+          <t>91.14x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7-Sep 13:29</t>
+          <t>7-Sep 19:58</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -486,22 +486,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Qualiance International NSE SMEO</t>
+          <t>Qualiance International NSE SMECT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹60 (47.24%) 50 ↓ / 60 ↑</t>
+          <t>₹65 (51.18%) 50 ↓ / 65 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>91.14x</t>
+          <t>208.45x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8-Sep</t>
+          <t>8-Sep GMP: 65</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7-Sep 19:58</t>
+          <t>8-Sep 12:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,73 +480,6 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Qualiance International NSE SMECT</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹65 (51.18%) 50 ↓ / 65 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>208.45x</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>₹45.11 Cr</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>4-Sep GMP: 55</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8-Sep GMP: 65</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>9-Sep</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>11-Sep</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>8-Sep 12:55</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,73 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Vinod Texworld NSE SMEO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹20 (21.28%) 4 ↓ / 20 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.35x</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹42.83 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9-Sep GMP: 20</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>11-Sep</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15-Sep</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>17-Sep</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10-Sep 12:55</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.35x</t>
+          <t>0.59x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10-Sep 12:55</t>
+          <t>10-Sep 18:32</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,73 +480,6 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Vinod Texworld NSE SMEO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹20 (21.28%) 4 ↓ / 20 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.59x</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>₹42.83 Cr</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>9-Sep GMP: 20</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>11-Sep</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>15-Sep</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>17-Sep</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>10-Sep 18:32</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>❌</t>
         </is>
       </c>
     </row>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,73 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Maharaja &amp; Speedex India BSE SMEO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹48 (25.81%) 15 ↓ / 48 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.48x</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹80.13 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>10-Sep GMP: 30</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15-Sep</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>18-Sep</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>13-Sep 13:30</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>
